--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902296</v>
+        <v>131902508</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>78932</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463633</v>
+        <v>463582</v>
       </c>
       <c r="R28" t="n">
-        <v>6788814</v>
+        <v>6788856</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,11 +3322,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131901760</v>
+        <v>131898255</v>
       </c>
       <c r="B29" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,16 +3359,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3384,19 +3379,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463848</v>
+        <v>464199</v>
       </c>
       <c r="R29" t="n">
-        <v>6789114</v>
+        <v>6788859</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,6 +3426,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3448,14 +3448,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131899185</v>
+        <v>131900413</v>
       </c>
       <c r="B30" t="n">
         <v>79266</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464113</v>
+        <v>464141</v>
       </c>
       <c r="R30" t="n">
-        <v>6788858</v>
+        <v>6788971</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902508</v>
+        <v>131902296</v>
       </c>
       <c r="B31" t="n">
-        <v>78932</v>
+        <v>79266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463582</v>
+        <v>463633</v>
       </c>
       <c r="R31" t="n">
-        <v>6788856</v>
+        <v>6788814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,6 +3623,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3649,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131902263</v>
+        <v>131901760</v>
       </c>
       <c r="B32" t="n">
-        <v>79856</v>
+        <v>57901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,34 +3665,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463633</v>
+        <v>463848</v>
       </c>
       <c r="R32" t="n">
-        <v>6788814</v>
+        <v>6789114</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,10 +3756,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131898255</v>
+        <v>131899185</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,39 +3767,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464199</v>
+        <v>464113</v>
       </c>
       <c r="R33" t="n">
-        <v>6788859</v>
+        <v>6788858</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,11 +3827,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131900413</v>
+        <v>131902263</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>79856</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,34 +3864,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464141</v>
+        <v>463633</v>
       </c>
       <c r="R34" t="n">
-        <v>6788971</v>
+        <v>6788814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902508</v>
+        <v>131902296</v>
       </c>
       <c r="B28" t="n">
-        <v>78932</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463582</v>
+        <v>463633</v>
       </c>
       <c r="R28" t="n">
-        <v>6788856</v>
+        <v>6788814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,6 +3322,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3348,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131898255</v>
+        <v>131901760</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,16 +3364,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3379,19 +3384,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464199</v>
+        <v>463848</v>
       </c>
       <c r="R29" t="n">
-        <v>6788859</v>
+        <v>6789114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,11 +3431,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3448,14 +3448,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131900413</v>
+        <v>131899185</v>
       </c>
       <c r="B30" t="n">
         <v>79266</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464141</v>
+        <v>464113</v>
       </c>
       <c r="R30" t="n">
-        <v>6788971</v>
+        <v>6788858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902296</v>
+        <v>131902508</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>78932</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463633</v>
+        <v>463582</v>
       </c>
       <c r="R31" t="n">
-        <v>6788814</v>
+        <v>6788856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3654,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131901760</v>
+        <v>131902263</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>79856</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463848</v>
+        <v>463633</v>
       </c>
       <c r="R32" t="n">
-        <v>6789114</v>
+        <v>6788814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,10 +3746,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131899185</v>
+        <v>131898255</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3767,34 +3757,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464113</v>
+        <v>464199</v>
       </c>
       <c r="R33" t="n">
-        <v>6788858</v>
+        <v>6788859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3827,6 +3822,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131902263</v>
+        <v>131900413</v>
       </c>
       <c r="B34" t="n">
-        <v>79856</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,34 +3864,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463633</v>
+        <v>464141</v>
       </c>
       <c r="R34" t="n">
-        <v>6788814</v>
+        <v>6788971</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131900374</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131898976</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131897243</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131897313</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131902048</v>
+        <v>131903249</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>57907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463710</v>
+        <v>464176</v>
       </c>
       <c r="R6" t="n">
-        <v>6788923</v>
+        <v>6789029</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,45 +1170,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131902624</v>
+        <v>131898011</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>57095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463597</v>
+        <v>464206</v>
       </c>
       <c r="R7" t="n">
-        <v>6788860</v>
+        <v>6788891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,17 +1265,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131903249</v>
+        <v>131902048</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>79026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,39 +1283,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464176</v>
+        <v>463710</v>
       </c>
       <c r="R8" t="n">
-        <v>6789029</v>
+        <v>6788923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131900839</v>
+        <v>131902624</v>
       </c>
       <c r="B9" t="n">
-        <v>78273</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464154</v>
+        <v>463597</v>
       </c>
       <c r="R9" t="n">
-        <v>6789027</v>
+        <v>6788860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,57 +1459,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131898011</v>
+        <v>131900839</v>
       </c>
       <c r="B10" t="n">
-        <v>57092</v>
+        <v>78276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464206</v>
+        <v>464154</v>
       </c>
       <c r="R10" t="n">
-        <v>6788891</v>
+        <v>6789027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902053</v>
+        <v>131902908</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>78935</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463710</v>
+        <v>463699</v>
       </c>
       <c r="R11" t="n">
-        <v>6788923</v>
+        <v>6788977</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902908</v>
+        <v>131902053</v>
       </c>
       <c r="B12" t="n">
-        <v>78932</v>
+        <v>79269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463699</v>
+        <v>463710</v>
       </c>
       <c r="R12" t="n">
-        <v>6788977</v>
+        <v>6788923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902164</v>
+        <v>131902512</v>
       </c>
       <c r="B13" t="n">
-        <v>79024</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463693</v>
+        <v>463582</v>
       </c>
       <c r="R13" t="n">
-        <v>6788840</v>
+        <v>6788856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902512</v>
+        <v>131902984</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1865,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463582</v>
+        <v>463793</v>
       </c>
       <c r="R14" t="n">
-        <v>6788856</v>
+        <v>6789072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,50 +1956,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131902984</v>
+        <v>131898830</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463793</v>
+        <v>464177</v>
       </c>
       <c r="R15" t="n">
-        <v>6789072</v>
+        <v>6788855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,57 +2051,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131898830</v>
+        <v>131902164</v>
       </c>
       <c r="B16" t="n">
-        <v>8454</v>
+        <v>79027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464177</v>
+        <v>463693</v>
       </c>
       <c r="R16" t="n">
-        <v>6788855</v>
+        <v>6788840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
         <v>131900199</v>
       </c>
       <c r="B17" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131898363</v>
+        <v>131903093</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,39 +2263,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464192</v>
+        <v>463928</v>
       </c>
       <c r="R18" t="n">
-        <v>6788879</v>
+        <v>6789135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,52 +2342,57 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131898938</v>
+        <v>131898363</v>
       </c>
       <c r="B19" t="n">
-        <v>79290</v>
+        <v>57907</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464168</v>
+        <v>464192</v>
       </c>
       <c r="R19" t="n">
-        <v>6788847</v>
+        <v>6788879</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,45 +2451,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131903093</v>
+        <v>131898938</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>79293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463928</v>
+        <v>464168</v>
       </c>
       <c r="R20" t="n">
-        <v>6789135</v>
+        <v>6788847</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2551,7 +2551,7 @@
         <v>131897316</v>
       </c>
       <c r="B21" t="n">
-        <v>81251</v>
+        <v>81254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>131901655</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131900445</v>
+        <v>131898053</v>
       </c>
       <c r="B23" t="n">
-        <v>8454</v>
+        <v>57095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,27 +2753,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2782,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464151</v>
+        <v>464192</v>
       </c>
       <c r="R23" t="n">
-        <v>6788971</v>
+        <v>6788879</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,6 +2822,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2847,7 +2856,7 @@
         <v>131899382</v>
       </c>
       <c r="B24" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2949,7 +2958,7 @@
         <v>131900297</v>
       </c>
       <c r="B25" t="n">
-        <v>78932</v>
+        <v>78935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3046,7 +3055,7 @@
         <v>131900843</v>
       </c>
       <c r="B26" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,10 +3149,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131898053</v>
+        <v>131900445</v>
       </c>
       <c r="B27" t="n">
-        <v>57092</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,31 +3160,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3184,10 +3189,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464192</v>
+        <v>464151</v>
       </c>
       <c r="R27" t="n">
-        <v>6788879</v>
+        <v>6788971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902508</v>
+        <v>131902296</v>
       </c>
       <c r="B28" t="n">
-        <v>78932</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463582</v>
+        <v>463633</v>
       </c>
       <c r="R28" t="n">
-        <v>6788856</v>
+        <v>6788814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,6 +3322,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3348,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131898255</v>
+        <v>131900413</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,39 +3364,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464199</v>
+        <v>464141</v>
       </c>
       <c r="R29" t="n">
-        <v>6788859</v>
+        <v>6788971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3424,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131900413</v>
+        <v>131898255</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,34 +3461,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464141</v>
+        <v>464199</v>
       </c>
       <c r="R30" t="n">
-        <v>6788971</v>
+        <v>6788859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,6 +3526,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,10 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902296</v>
+        <v>131899185</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,14 +3588,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463633</v>
+        <v>464113</v>
       </c>
       <c r="R31" t="n">
-        <v>6788814</v>
+        <v>6788858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,11 +3630,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3647,17 +3647,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131901760</v>
+        <v>131902508</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>78935</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3665,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463848</v>
+        <v>463582</v>
       </c>
       <c r="R32" t="n">
-        <v>6789114</v>
+        <v>6788856</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131899185</v>
+        <v>131901760</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3767,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464113</v>
+        <v>463848</v>
       </c>
       <c r="R33" t="n">
-        <v>6788858</v>
+        <v>6789114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3856,7 +3856,7 @@
         <v>131902263</v>
       </c>
       <c r="B34" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>131902169</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>131900601</v>
       </c>
       <c r="B36" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>131901653</v>
       </c>
       <c r="B37" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>131902458</v>
       </c>
       <c r="B38" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>131901996</v>
       </c>
       <c r="B39" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4445,54 +4445,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131902617</v>
+        <v>131900207</v>
       </c>
       <c r="B40" t="n">
-        <v>8454</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463597</v>
+        <v>464122</v>
       </c>
       <c r="R40" t="n">
-        <v>6788860</v>
+        <v>6788896</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4527,11 +4518,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På tre torrtallar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4549,17 +4535,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131900207</v>
+        <v>131900410</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>78935</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,21 +4553,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4591,10 +4577,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464122</v>
+        <v>464141</v>
       </c>
       <c r="R41" t="n">
-        <v>6788896</v>
+        <v>6788971</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,45 +4639,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131900410</v>
+        <v>131902617</v>
       </c>
       <c r="B42" t="n">
-        <v>78932</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464141</v>
+        <v>463597</v>
       </c>
       <c r="R42" t="n">
-        <v>6788971</v>
+        <v>6788860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4721,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tre torrtallar</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
         <v>131902911</v>
       </c>
       <c r="B43" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>131900448</v>
       </c>
       <c r="B44" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131901998</v>
+        <v>131898831</v>
       </c>
       <c r="B45" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,14 +4975,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463740</v>
+        <v>464177</v>
       </c>
       <c r="R45" t="n">
-        <v>6788944</v>
+        <v>6788855</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131900323</v>
+        <v>131898366</v>
       </c>
       <c r="B46" t="n">
-        <v>79298</v>
+        <v>79269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5052,21 +5052,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464130</v>
+        <v>464192</v>
       </c>
       <c r="R46" t="n">
-        <v>6788932</v>
+        <v>6788879</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131898831</v>
+        <v>131900323</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>79301</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464177</v>
+        <v>464130</v>
       </c>
       <c r="R47" t="n">
-        <v>6788855</v>
+        <v>6788932</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131898366</v>
+        <v>131901998</v>
       </c>
       <c r="B48" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464192</v>
+        <v>463740</v>
       </c>
       <c r="R48" t="n">
-        <v>6788879</v>
+        <v>6788944</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131899796</v>
+        <v>131899308</v>
       </c>
       <c r="B49" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464098</v>
+        <v>464087</v>
       </c>
       <c r="R49" t="n">
-        <v>6788894</v>
+        <v>6788862</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899308</v>
+        <v>131899796</v>
       </c>
       <c r="B50" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464087</v>
+        <v>464098</v>
       </c>
       <c r="R50" t="n">
-        <v>6788862</v>
+        <v>6788894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
         <v>131902049</v>
       </c>
       <c r="B51" t="n">
-        <v>79024</v>
+        <v>79027</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131900856</v>
+        <v>131898971</v>
       </c>
       <c r="B52" t="n">
-        <v>57901</v>
+        <v>78935</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,39 +5644,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464154</v>
+        <v>464168</v>
       </c>
       <c r="R52" t="n">
-        <v>6789027</v>
+        <v>6788847</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5735,10 +5730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131902988</v>
+        <v>131898074</v>
       </c>
       <c r="B53" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,17 +5761,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463793</v>
+        <v>464189</v>
       </c>
       <c r="R53" t="n">
-        <v>6789072</v>
+        <v>6788866</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5806,6 +5801,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131903258</v>
+        <v>131902988</v>
       </c>
       <c r="B54" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,14 +5863,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464176</v>
+        <v>463793</v>
       </c>
       <c r="R54" t="n">
-        <v>6789029</v>
+        <v>6789072</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131898971</v>
+        <v>131903258</v>
       </c>
       <c r="B55" t="n">
-        <v>78932</v>
+        <v>79269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464168</v>
+        <v>464176</v>
       </c>
       <c r="R55" t="n">
-        <v>6788847</v>
+        <v>6789029</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6019,17 +6019,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131898074</v>
+        <v>131900856</v>
       </c>
       <c r="B56" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,37 +6037,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464154</v>
       </c>
       <c r="R56" t="n">
-        <v>6788866</v>
+        <v>6789027</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6097,11 +6102,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6131,7 +6131,7 @@
         <v>131900329</v>
       </c>
       <c r="B57" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>131903171</v>
       </c>
       <c r="B58" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131899801</v>
+        <v>131897390</v>
       </c>
       <c r="B59" t="n">
-        <v>79266</v>
+        <v>78935</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464098</v>
+        <v>464224</v>
       </c>
       <c r="R59" t="n">
-        <v>6788894</v>
+        <v>6788964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131897390</v>
+        <v>131899801</v>
       </c>
       <c r="B60" t="n">
-        <v>78932</v>
+        <v>79269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464224</v>
+        <v>464098</v>
       </c>
       <c r="R60" t="n">
-        <v>6788964</v>
+        <v>6788894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6519,7 +6519,7 @@
         <v>131900650</v>
       </c>
       <c r="B61" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,45 +6618,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131903090</v>
+        <v>131901744</v>
       </c>
       <c r="B62" t="n">
-        <v>79856</v>
+        <v>8455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463928</v>
+        <v>463848</v>
       </c>
       <c r="R62" t="n">
-        <v>6789135</v>
+        <v>6789114</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6718,7 +6723,7 @@
         <v>131901955</v>
       </c>
       <c r="B63" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,53 +6817,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131901744</v>
+        <v>131902815</v>
       </c>
       <c r="B64" t="n">
-        <v>8454</v>
+        <v>79269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>463848</v>
+        <v>463654</v>
       </c>
       <c r="R64" t="n">
-        <v>6789114</v>
+        <v>6788918</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6888,6 +6888,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6914,10 +6919,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131902815</v>
+        <v>131900379</v>
       </c>
       <c r="B65" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6945,17 +6950,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463654</v>
+        <v>464130</v>
       </c>
       <c r="R65" t="n">
-        <v>6788918</v>
+        <v>6788950</v>
       </c>
       <c r="S65" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6985,11 +6990,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7009,52 +7009,52 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131900379</v>
+        <v>131902904</v>
       </c>
       <c r="B66" t="n">
-        <v>79266</v>
+        <v>97918</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464130</v>
+        <v>463699</v>
       </c>
       <c r="R66" t="n">
-        <v>6788950</v>
+        <v>6788977</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,39 +7106,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131902904</v>
+        <v>131903090</v>
       </c>
       <c r="B67" t="n">
-        <v>97915</v>
+        <v>79859</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463699</v>
+        <v>463928</v>
       </c>
       <c r="R67" t="n">
-        <v>6788977</v>
+        <v>6789135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131900191</v>
+        <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>57901</v>
+        <v>79888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,39 +7221,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464122</v>
+        <v>464211</v>
       </c>
       <c r="R68" t="n">
-        <v>6788896</v>
+        <v>6788946</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,10 +7307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131897699</v>
+        <v>131898911</v>
       </c>
       <c r="B69" t="n">
-        <v>79885</v>
+        <v>79269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7323,21 +7318,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464211</v>
+        <v>464178</v>
       </c>
       <c r="R69" t="n">
-        <v>6788946</v>
+        <v>6788843</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,10 +7404,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131898911</v>
+        <v>131901872</v>
       </c>
       <c r="B70" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,17 +7435,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464178</v>
+        <v>463779</v>
       </c>
       <c r="R70" t="n">
-        <v>6788843</v>
+        <v>6789025</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7480,6 +7475,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7499,17 +7499,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131901872</v>
+        <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79266</v>
+        <v>79888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7517,37 +7517,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>463779</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6789025</v>
+        <v>6788922</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,11 +7577,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7601,17 +7596,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900290</v>
+        <v>131900191</v>
       </c>
       <c r="B72" t="n">
-        <v>79885</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7619,34 +7614,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464132</v>
+        <v>464122</v>
       </c>
       <c r="R72" t="n">
-        <v>6788922</v>
+        <v>6788896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,53 +7705,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131900596</v>
+        <v>131902839</v>
       </c>
       <c r="B73" t="n">
-        <v>57904</v>
+        <v>79293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464194</v>
+        <v>463654</v>
       </c>
       <c r="R73" t="n">
-        <v>6788999</v>
+        <v>6788918</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7800,39 +7795,39 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131902839</v>
+        <v>131901762</v>
       </c>
       <c r="B74" t="n">
-        <v>79290</v>
+        <v>79269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7842,13 +7837,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>463654</v>
+        <v>463848</v>
       </c>
       <c r="R74" t="n">
-        <v>6788918</v>
+        <v>6789114</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7904,32 +7899,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131897325</v>
+        <v>131900248</v>
       </c>
       <c r="B75" t="n">
-        <v>79290</v>
+        <v>79269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7939,13 +7934,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464224</v>
+        <v>464139</v>
       </c>
       <c r="R75" t="n">
-        <v>6788964</v>
+        <v>6788911</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7975,6 +7970,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8001,10 +8001,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131901762</v>
+        <v>131900596</v>
       </c>
       <c r="B76" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8012,34 +8012,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>463848</v>
+        <v>464194</v>
       </c>
       <c r="R76" t="n">
-        <v>6789114</v>
+        <v>6788999</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8091,39 +8096,39 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131898908</v>
+        <v>131897325</v>
       </c>
       <c r="B77" t="n">
-        <v>79023</v>
+        <v>79293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8133,10 +8138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464178</v>
+        <v>464224</v>
       </c>
       <c r="R77" t="n">
-        <v>6788843</v>
+        <v>6788964</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8195,10 +8200,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131900248</v>
+        <v>131898908</v>
       </c>
       <c r="B78" t="n">
-        <v>79266</v>
+        <v>79026</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8206,21 +8211,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8230,13 +8235,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464139</v>
+        <v>464178</v>
       </c>
       <c r="R78" t="n">
-        <v>6788911</v>
+        <v>6788843</v>
       </c>
       <c r="S78" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8266,11 +8271,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131900374</v>
+        <v>131898976</v>
       </c>
       <c r="B2" t="n">
-        <v>79026</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464130</v>
+        <v>464168</v>
       </c>
       <c r="R2" t="n">
-        <v>6788950</v>
+        <v>6788847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131898976</v>
+        <v>131897243</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464168</v>
+        <v>464220</v>
       </c>
       <c r="R3" t="n">
-        <v>6788847</v>
+        <v>6788950</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet. Rikligt med brandljud</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131897243</v>
+        <v>131900374</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>79031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464220</v>
+        <v>464130</v>
       </c>
       <c r="R4" t="n">
         <v>6788950</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet. Rikligt med brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131897313</v>
+        <v>131902048</v>
       </c>
       <c r="B5" t="n">
-        <v>79859</v>
+        <v>79031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464224</v>
+        <v>463710</v>
       </c>
       <c r="R5" t="n">
-        <v>6788964</v>
+        <v>6788923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1061,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131903249</v>
+        <v>131902624</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1079,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464176</v>
+        <v>463597</v>
       </c>
       <c r="R6" t="n">
-        <v>6789029</v>
+        <v>6788860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131898011</v>
+        <v>131900839</v>
       </c>
       <c r="B7" t="n">
-        <v>57095</v>
+        <v>78281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464206</v>
+        <v>464154</v>
       </c>
       <c r="R7" t="n">
-        <v>6788891</v>
+        <v>6789027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,45 +1262,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131902048</v>
+        <v>131898011</v>
       </c>
       <c r="B8" t="n">
-        <v>79026</v>
+        <v>57100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463710</v>
+        <v>464206</v>
       </c>
       <c r="R8" t="n">
-        <v>6788923</v>
+        <v>6788891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,17 +1357,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131902624</v>
+        <v>131903249</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463597</v>
+        <v>464176</v>
       </c>
       <c r="R9" t="n">
-        <v>6788860</v>
+        <v>6789029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131900839</v>
+        <v>131897313</v>
       </c>
       <c r="B10" t="n">
-        <v>78276</v>
+        <v>79864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464154</v>
+        <v>464224</v>
       </c>
       <c r="R10" t="n">
-        <v>6789027</v>
+        <v>6788964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902908</v>
+        <v>131902164</v>
       </c>
       <c r="B11" t="n">
-        <v>78935</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463699</v>
+        <v>463693</v>
       </c>
       <c r="R11" t="n">
-        <v>6788977</v>
+        <v>6788840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902053</v>
+        <v>131902984</v>
       </c>
       <c r="B12" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,34 +1671,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463710</v>
+        <v>463793</v>
       </c>
       <c r="R12" t="n">
-        <v>6788923</v>
+        <v>6789072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902512</v>
+        <v>131902053</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463582</v>
+        <v>463710</v>
       </c>
       <c r="R13" t="n">
-        <v>6788856</v>
+        <v>6788923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902984</v>
+        <v>131902512</v>
       </c>
       <c r="B14" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,39 +1870,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463793</v>
+        <v>463582</v>
       </c>
       <c r="R14" t="n">
-        <v>6789072</v>
+        <v>6788856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,50 +1956,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131898830</v>
+        <v>131902908</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>78940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464177</v>
+        <v>463699</v>
       </c>
       <c r="R15" t="n">
-        <v>6788855</v>
+        <v>6788977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,52 +2046,57 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131902164</v>
+        <v>131898830</v>
       </c>
       <c r="B16" t="n">
-        <v>79027</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463693</v>
+        <v>464177</v>
       </c>
       <c r="R16" t="n">
-        <v>6788840</v>
+        <v>6788855</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2252,45 +2252,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131903093</v>
+        <v>131898938</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463928</v>
+        <v>464168</v>
       </c>
       <c r="R18" t="n">
-        <v>6789135</v>
+        <v>6788847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,17 +2342,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131898363</v>
+        <v>131903093</v>
       </c>
       <c r="B19" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,39 +2360,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464192</v>
+        <v>463928</v>
       </c>
       <c r="R19" t="n">
-        <v>6788879</v>
+        <v>6789135</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,52 +2439,57 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131898938</v>
+        <v>131898363</v>
       </c>
       <c r="B20" t="n">
-        <v>79293</v>
+        <v>57912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464168</v>
+        <v>464192</v>
       </c>
       <c r="R20" t="n">
-        <v>6788847</v>
+        <v>6788879</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131897316</v>
+        <v>131901655</v>
       </c>
       <c r="B21" t="n">
-        <v>81254</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464224</v>
+        <v>463892</v>
       </c>
       <c r="R21" t="n">
-        <v>6788964</v>
+        <v>6789126</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131901655</v>
+        <v>131897316</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>81259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463892</v>
+        <v>464224</v>
       </c>
       <c r="R22" t="n">
-        <v>6789126</v>
+        <v>6788964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,42 +2742,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131898053</v>
+        <v>131899382</v>
       </c>
       <c r="B23" t="n">
-        <v>57095</v>
+        <v>57909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2786,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464192</v>
+        <v>464087</v>
       </c>
       <c r="R23" t="n">
-        <v>6788879</v>
+        <v>6788862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2822,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2853,38 +2844,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131899382</v>
+        <v>131900445</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2893,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464087</v>
+        <v>464151</v>
       </c>
       <c r="R24" t="n">
-        <v>6788862</v>
+        <v>6788971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,7 +2949,7 @@
         <v>131900297</v>
       </c>
       <c r="B25" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,45 +3043,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131900843</v>
+        <v>131898053</v>
       </c>
       <c r="B26" t="n">
-        <v>79859</v>
+        <v>57100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464154</v>
+        <v>464192</v>
       </c>
       <c r="R26" t="n">
-        <v>6789027</v>
+        <v>6788879</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,6 +3123,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3149,50 +3154,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131900445</v>
+        <v>131900843</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>79864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464151</v>
+        <v>464154</v>
       </c>
       <c r="R27" t="n">
-        <v>6788971</v>
+        <v>6789027</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902296</v>
+        <v>131902508</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>78940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463633</v>
+        <v>463582</v>
       </c>
       <c r="R28" t="n">
-        <v>6788814</v>
+        <v>6788856</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,11 +3322,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131900413</v>
+        <v>131901760</v>
       </c>
       <c r="B29" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,34 +3359,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464141</v>
+        <v>463848</v>
       </c>
       <c r="R29" t="n">
-        <v>6788971</v>
+        <v>6789114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3443,17 +3443,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131898255</v>
+        <v>131899185</v>
       </c>
       <c r="B30" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,39 +3461,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464113</v>
       </c>
       <c r="R30" t="n">
-        <v>6788859</v>
+        <v>6788858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,11 +3521,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3557,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131899185</v>
+        <v>131902296</v>
       </c>
       <c r="B31" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,14 +3578,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464113</v>
+        <v>463633</v>
       </c>
       <c r="R31" t="n">
-        <v>6788858</v>
+        <v>6788814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,6 +3620,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3647,17 +3642,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131902508</v>
+        <v>131900413</v>
       </c>
       <c r="B32" t="n">
-        <v>78935</v>
+        <v>79274</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,34 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463582</v>
+        <v>464141</v>
       </c>
       <c r="R32" t="n">
-        <v>6788856</v>
+        <v>6788971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,17 +3739,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131901760</v>
+        <v>131898255</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>57912</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,16 +3757,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3782,19 +3777,19 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463848</v>
+        <v>464199</v>
       </c>
       <c r="R33" t="n">
-        <v>6789114</v>
+        <v>6788859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3829,6 +3824,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3856,7 +3856,7 @@
         <v>131902263</v>
       </c>
       <c r="B34" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>131902169</v>
       </c>
       <c r="B35" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>131900601</v>
       </c>
       <c r="B36" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>131901653</v>
       </c>
       <c r="B37" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>131902458</v>
       </c>
       <c r="B38" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>131901996</v>
       </c>
       <c r="B39" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>131900207</v>
       </c>
       <c r="B40" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>131900410</v>
       </c>
       <c r="B41" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>131902911</v>
       </c>
       <c r="B43" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>131900448</v>
       </c>
       <c r="B44" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>131898831</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>131898366</v>
       </c>
       <c r="B46" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>131900323</v>
       </c>
       <c r="B47" t="n">
-        <v>79301</v>
+        <v>79306</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>131901998</v>
       </c>
       <c r="B48" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131899308</v>
+        <v>131899796</v>
       </c>
       <c r="B49" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464087</v>
+        <v>464098</v>
       </c>
       <c r="R49" t="n">
-        <v>6788862</v>
+        <v>6788894</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899796</v>
+        <v>131899308</v>
       </c>
       <c r="B50" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464098</v>
+        <v>464087</v>
       </c>
       <c r="R50" t="n">
-        <v>6788894</v>
+        <v>6788862</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
         <v>131902049</v>
       </c>
       <c r="B51" t="n">
-        <v>79027</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131898971</v>
+        <v>131898074</v>
       </c>
       <c r="B52" t="n">
-        <v>78935</v>
+        <v>79274</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5668,13 +5668,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464168</v>
+        <v>464189</v>
       </c>
       <c r="R52" t="n">
-        <v>6788847</v>
+        <v>6788866</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5704,6 +5704,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5730,10 +5735,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131898074</v>
+        <v>131898971</v>
       </c>
       <c r="B53" t="n">
-        <v>79269</v>
+        <v>78940</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5741,21 +5746,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5765,13 +5770,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464189</v>
+        <v>464168</v>
       </c>
       <c r="R53" t="n">
-        <v>6788866</v>
+        <v>6788847</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5801,11 +5806,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5835,7 +5835,7 @@
         <v>131902988</v>
       </c>
       <c r="B54" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>131903258</v>
       </c>
       <c r="B55" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>131900856</v>
       </c>
       <c r="B56" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>131900329</v>
       </c>
       <c r="B57" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>131903171</v>
       </c>
       <c r="B58" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131897390</v>
+        <v>131900650</v>
       </c>
       <c r="B59" t="n">
-        <v>78935</v>
+        <v>79274</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,13 +6357,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464224</v>
+        <v>464205</v>
       </c>
       <c r="R59" t="n">
-        <v>6788964</v>
+        <v>6789008</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6393,6 +6393,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6419,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131899801</v>
+        <v>131897390</v>
       </c>
       <c r="B60" t="n">
-        <v>79269</v>
+        <v>78940</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6454,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464098</v>
+        <v>464224</v>
       </c>
       <c r="R60" t="n">
-        <v>6788894</v>
+        <v>6788964</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6516,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131900650</v>
+        <v>131899801</v>
       </c>
       <c r="B61" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,13 +6556,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464205</v>
+        <v>464098</v>
       </c>
       <c r="R61" t="n">
-        <v>6789008</v>
+        <v>6788894</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6587,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6618,50 +6618,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131901744</v>
+        <v>131901955</v>
       </c>
       <c r="B62" t="n">
-        <v>8455</v>
+        <v>79274</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463848</v>
+        <v>463761</v>
       </c>
       <c r="R62" t="n">
-        <v>6789114</v>
+        <v>6789030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131901955</v>
+        <v>131902815</v>
       </c>
       <c r="B63" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,13 +6750,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463761</v>
+        <v>463654</v>
       </c>
       <c r="R63" t="n">
-        <v>6789030</v>
+        <v>6788918</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6791,6 +6786,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131902815</v>
+        <v>131900379</v>
       </c>
       <c r="B64" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6848,17 +6848,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>463654</v>
+        <v>464130</v>
       </c>
       <c r="R64" t="n">
-        <v>6788918</v>
+        <v>6788950</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6888,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6912,52 +6907,57 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131900379</v>
+        <v>131901744</v>
       </c>
       <c r="B65" t="n">
-        <v>79269</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464130</v>
+        <v>463848</v>
       </c>
       <c r="R65" t="n">
-        <v>6788950</v>
+        <v>6789114</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
         <v>131902904</v>
       </c>
       <c r="B66" t="n">
-        <v>97918</v>
+        <v>97923</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>131903090</v>
       </c>
       <c r="B67" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>131898911</v>
       </c>
       <c r="B69" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>131901872</v>
       </c>
       <c r="B70" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>131900191</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131902839</v>
       </c>
       <c r="B73" t="n">
-        <v>79293</v>
+        <v>79298</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131901762</v>
       </c>
       <c r="B74" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>131900248</v>
       </c>
       <c r="B75" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8001,50 +8001,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131900596</v>
+        <v>131897325</v>
       </c>
       <c r="B76" t="n">
-        <v>57907</v>
+        <v>79298</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464194</v>
+        <v>464224</v>
       </c>
       <c r="R76" t="n">
-        <v>6788999</v>
+        <v>6788964</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8103,45 +8098,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131897325</v>
+        <v>131900596</v>
       </c>
       <c r="B77" t="n">
-        <v>79293</v>
+        <v>57912</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464224</v>
+        <v>464194</v>
       </c>
       <c r="R77" t="n">
-        <v>6788964</v>
+        <v>6788999</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,7 +8203,7 @@
         <v>131898908</v>
       </c>
       <c r="B78" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902984</v>
+        <v>131902908</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>78940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,39 +1671,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463793</v>
+        <v>463699</v>
       </c>
       <c r="R12" t="n">
-        <v>6789072</v>
+        <v>6788977</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902053</v>
+        <v>131902984</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,34 +1768,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463710</v>
+        <v>463793</v>
       </c>
       <c r="R13" t="n">
-        <v>6788923</v>
+        <v>6789072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902512</v>
+        <v>131902053</v>
       </c>
       <c r="B14" t="n">
         <v>79274</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463582</v>
+        <v>463710</v>
       </c>
       <c r="R14" t="n">
-        <v>6788856</v>
+        <v>6788923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131902908</v>
+        <v>131902512</v>
       </c>
       <c r="B15" t="n">
-        <v>78940</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463699</v>
+        <v>463582</v>
       </c>
       <c r="R15" t="n">
-        <v>6788977</v>
+        <v>6788856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131898074</v>
+        <v>131898971</v>
       </c>
       <c r="B52" t="n">
-        <v>79274</v>
+        <v>78940</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5668,13 +5668,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464189</v>
+        <v>464168</v>
       </c>
       <c r="R52" t="n">
-        <v>6788866</v>
+        <v>6788847</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5704,11 +5704,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5735,10 +5730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131898971</v>
+        <v>131898074</v>
       </c>
       <c r="B53" t="n">
-        <v>78940</v>
+        <v>79274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5746,21 +5741,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5770,13 +5765,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464168</v>
+        <v>464189</v>
       </c>
       <c r="R53" t="n">
-        <v>6788847</v>
+        <v>6788866</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5806,6 +5801,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131898976</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131897243</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131900374</v>
       </c>
       <c r="B4" t="n">
-        <v>79031</v>
+        <v>79033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131902048</v>
+        <v>131903249</v>
       </c>
       <c r="B5" t="n">
-        <v>79031</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +982,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463710</v>
+        <v>464176</v>
       </c>
       <c r="R5" t="n">
-        <v>6788923</v>
+        <v>6789029</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,45 +1073,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131902624</v>
+        <v>131898011</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>57102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463597</v>
+        <v>464206</v>
       </c>
       <c r="R6" t="n">
-        <v>6788860</v>
+        <v>6788891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,17 +1168,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131900839</v>
+        <v>131897313</v>
       </c>
       <c r="B7" t="n">
-        <v>78281</v>
+        <v>79866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464154</v>
+        <v>464224</v>
       </c>
       <c r="R7" t="n">
-        <v>6789027</v>
+        <v>6788964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,50 +1272,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131898011</v>
+        <v>131902048</v>
       </c>
       <c r="B8" t="n">
-        <v>57100</v>
+        <v>79033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464206</v>
+        <v>463710</v>
       </c>
       <c r="R8" t="n">
-        <v>6788891</v>
+        <v>6788923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,17 +1362,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131903249</v>
+        <v>131902624</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,39 +1380,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464176</v>
+        <v>463597</v>
       </c>
       <c r="R9" t="n">
-        <v>6789029</v>
+        <v>6788860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131897313</v>
+        <v>131900839</v>
       </c>
       <c r="B10" t="n">
-        <v>79864</v>
+        <v>78283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464224</v>
+        <v>464154</v>
       </c>
       <c r="R10" t="n">
-        <v>6788964</v>
+        <v>6789027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902164</v>
+        <v>131902053</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463693</v>
+        <v>463710</v>
       </c>
       <c r="R11" t="n">
-        <v>6788840</v>
+        <v>6788923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902908</v>
+        <v>131902512</v>
       </c>
       <c r="B12" t="n">
-        <v>78940</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463699</v>
+        <v>463582</v>
       </c>
       <c r="R12" t="n">
-        <v>6788977</v>
+        <v>6788856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
         <v>131902984</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902053</v>
+        <v>131902908</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>78942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463710</v>
+        <v>463699</v>
       </c>
       <c r="R14" t="n">
-        <v>6788923</v>
+        <v>6788977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131902512</v>
+        <v>131902164</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463582</v>
+        <v>463693</v>
       </c>
       <c r="R15" t="n">
-        <v>6788856</v>
+        <v>6788840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
         <v>131898938</v>
       </c>
       <c r="B18" t="n">
-        <v>79298</v>
+        <v>79300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131903093</v>
+        <v>131898363</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,34 +2360,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463928</v>
+        <v>464192</v>
       </c>
       <c r="R19" t="n">
-        <v>6789135</v>
+        <v>6788879</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,17 +2444,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131898363</v>
+        <v>131903093</v>
       </c>
       <c r="B20" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,39 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464192</v>
+        <v>463928</v>
       </c>
       <c r="R20" t="n">
-        <v>6788879</v>
+        <v>6789135</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2551,7 +2551,7 @@
         <v>131901655</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>131897316</v>
       </c>
       <c r="B22" t="n">
-        <v>81259</v>
+        <v>81261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131899382</v>
+        <v>131900297</v>
       </c>
       <c r="B23" t="n">
-        <v>57909</v>
+        <v>78942</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,39 +2753,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464087</v>
+        <v>464132</v>
       </c>
       <c r="R23" t="n">
-        <v>6788862</v>
+        <v>6788922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,45 +2941,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131900297</v>
+        <v>131898053</v>
       </c>
       <c r="B25" t="n">
-        <v>78940</v>
+        <v>57102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464132</v>
+        <v>464192</v>
       </c>
       <c r="R25" t="n">
-        <v>6788922</v>
+        <v>6788879</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,6 +3021,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,42 +3052,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131898053</v>
+        <v>131899382</v>
       </c>
       <c r="B26" t="n">
-        <v>57100</v>
+        <v>57911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3087,10 +3092,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464192</v>
+        <v>464087</v>
       </c>
       <c r="R26" t="n">
-        <v>6788879</v>
+        <v>6788862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,11 +3128,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3157,7 +3157,7 @@
         <v>131900843</v>
       </c>
       <c r="B27" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>131902508</v>
       </c>
       <c r="B28" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131901760</v>
+        <v>131902296</v>
       </c>
       <c r="B29" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,39 +3359,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463848</v>
+        <v>463633</v>
       </c>
       <c r="R29" t="n">
-        <v>6789114</v>
+        <v>6788814</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,6 +3419,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131899185</v>
+        <v>131900413</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464113</v>
+        <v>464141</v>
       </c>
       <c r="R30" t="n">
-        <v>6788858</v>
+        <v>6788971</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902296</v>
+        <v>131901760</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,34 +3558,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463633</v>
+        <v>463848</v>
       </c>
       <c r="R31" t="n">
-        <v>6788814</v>
+        <v>6789114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131900413</v>
+        <v>131902263</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>79866</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,34 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464141</v>
+        <v>463633</v>
       </c>
       <c r="R32" t="n">
-        <v>6788971</v>
+        <v>6788814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131898255</v>
+        <v>131899185</v>
       </c>
       <c r="B33" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,39 +3757,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464199</v>
+        <v>464113</v>
       </c>
       <c r="R33" t="n">
-        <v>6788859</v>
+        <v>6788858</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,11 +3817,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,10 +3843,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131902263</v>
+        <v>131898255</v>
       </c>
       <c r="B34" t="n">
-        <v>79864</v>
+        <v>57914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,34 +3854,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463633</v>
+        <v>464199</v>
       </c>
       <c r="R34" t="n">
-        <v>6788814</v>
+        <v>6788859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3926,6 +3921,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
         <v>131902169</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>131900601</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>131901653</v>
       </c>
       <c r="B37" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>131902458</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>131901996</v>
       </c>
       <c r="B39" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131900207</v>
+        <v>131900410</v>
       </c>
       <c r="B40" t="n">
-        <v>79274</v>
+        <v>78942</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4456,21 +4456,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464122</v>
+        <v>464141</v>
       </c>
       <c r="R40" t="n">
-        <v>6788896</v>
+        <v>6788971</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131900410</v>
+        <v>131900207</v>
       </c>
       <c r="B41" t="n">
-        <v>78940</v>
+        <v>79276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4553,21 +4553,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464141</v>
+        <v>464122</v>
       </c>
       <c r="R41" t="n">
-        <v>6788971</v>
+        <v>6788896</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
         <v>131902911</v>
       </c>
       <c r="B43" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>131900448</v>
       </c>
       <c r="B44" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>131898831</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
         <v>131898366</v>
       </c>
       <c r="B46" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>131900323</v>
       </c>
       <c r="B47" t="n">
-        <v>79306</v>
+        <v>79308</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>131901998</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131899796</v>
+        <v>131902049</v>
       </c>
       <c r="B49" t="n">
-        <v>57912</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,39 +5343,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464098</v>
+        <v>463710</v>
       </c>
       <c r="R49" t="n">
-        <v>6788894</v>
+        <v>6788923</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,17 +5422,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899308</v>
+        <v>131899796</v>
       </c>
       <c r="B50" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464087</v>
+        <v>464098</v>
       </c>
       <c r="R50" t="n">
-        <v>6788862</v>
+        <v>6788894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5529,17 +5524,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131902049</v>
+        <v>131899308</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>57914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5547,34 +5542,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463710</v>
+        <v>464087</v>
       </c>
       <c r="R51" t="n">
-        <v>6788923</v>
+        <v>6788862</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         <v>131898971</v>
       </c>
       <c r="B52" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>131898074</v>
       </c>
       <c r="B53" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131902988</v>
+        <v>131903258</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,14 +5863,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463793</v>
+        <v>464176</v>
       </c>
       <c r="R54" t="n">
-        <v>6789072</v>
+        <v>6789029</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131903258</v>
+        <v>131900856</v>
       </c>
       <c r="B55" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,34 +5940,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464176</v>
+        <v>464154</v>
       </c>
       <c r="R55" t="n">
-        <v>6789029</v>
+        <v>6789027</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6019,17 +6024,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131900856</v>
+        <v>131902988</v>
       </c>
       <c r="B56" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,39 +6042,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464154</v>
+        <v>463793</v>
       </c>
       <c r="R56" t="n">
-        <v>6789027</v>
+        <v>6789072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>131900329</v>
       </c>
       <c r="B57" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>131903171</v>
       </c>
       <c r="B58" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131900650</v>
+        <v>131897390</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>78942</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,13 +6357,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464205</v>
+        <v>464224</v>
       </c>
       <c r="R59" t="n">
-        <v>6789008</v>
+        <v>6788964</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6393,11 +6393,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131897390</v>
+        <v>131899801</v>
       </c>
       <c r="B60" t="n">
-        <v>78940</v>
+        <v>79276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6430,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6454,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464224</v>
+        <v>464098</v>
       </c>
       <c r="R60" t="n">
-        <v>6788964</v>
+        <v>6788894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,17 +6509,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131899801</v>
+        <v>131900650</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,13 +6551,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464098</v>
+        <v>464205</v>
       </c>
       <c r="R61" t="n">
-        <v>6788894</v>
+        <v>6789008</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6592,6 +6587,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6621,7 +6621,7 @@
         <v>131901955</v>
       </c>
       <c r="B62" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>131902815</v>
       </c>
       <c r="B63" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>131900379</v>
       </c>
       <c r="B64" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131901744</v>
+        <v>131902904</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>97925</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,39 +6925,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>221941</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463848</v>
+        <v>463699</v>
       </c>
       <c r="R65" t="n">
-        <v>6789114</v>
+        <v>6788977</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7016,32 +7011,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131902904</v>
+        <v>131903090</v>
       </c>
       <c r="B66" t="n">
-        <v>97923</v>
+        <v>79866</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7051,10 +7046,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463699</v>
+        <v>463928</v>
       </c>
       <c r="R66" t="n">
-        <v>6788977</v>
+        <v>6789135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7113,45 +7108,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131903090</v>
+        <v>131901744</v>
       </c>
       <c r="B67" t="n">
-        <v>79864</v>
+        <v>8455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463928</v>
+        <v>463848</v>
       </c>
       <c r="R67" t="n">
-        <v>6789135</v>
+        <v>6789114</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7307,10 +7307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131898911</v>
+        <v>131900191</v>
       </c>
       <c r="B69" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7318,34 +7318,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464178</v>
+        <v>464122</v>
       </c>
       <c r="R69" t="n">
-        <v>6788843</v>
+        <v>6788896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7407,7 +7412,7 @@
         <v>131901872</v>
       </c>
       <c r="B70" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7514,7 @@
         <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7603,10 +7608,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900191</v>
+        <v>131898911</v>
       </c>
       <c r="B72" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7614,39 +7619,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464122</v>
+        <v>464178</v>
       </c>
       <c r="R72" t="n">
-        <v>6788896</v>
+        <v>6788843</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,10 +7705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131902839</v>
+        <v>131897325</v>
       </c>
       <c r="B73" t="n">
-        <v>79298</v>
+        <v>79300</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7736,17 +7736,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>463654</v>
+        <v>464224</v>
       </c>
       <c r="R73" t="n">
-        <v>6788918</v>
+        <v>6788964</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7795,17 +7795,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131901762</v>
+        <v>131898908</v>
       </c>
       <c r="B74" t="n">
-        <v>79274</v>
+        <v>79033</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7813,34 +7813,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>463848</v>
+        <v>464178</v>
       </c>
       <c r="R74" t="n">
-        <v>6789114</v>
+        <v>6788843</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7892,52 +7892,52 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131900248</v>
+        <v>131902839</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>79300</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464139</v>
+        <v>463654</v>
       </c>
       <c r="R75" t="n">
-        <v>6788911</v>
+        <v>6788918</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -7972,11 +7972,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -7994,52 +7989,52 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131897325</v>
+        <v>131901762</v>
       </c>
       <c r="B76" t="n">
-        <v>79298</v>
+        <v>79276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464224</v>
+        <v>463848</v>
       </c>
       <c r="R76" t="n">
-        <v>6788964</v>
+        <v>6789114</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8091,17 +8086,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131900596</v>
+        <v>131900248</v>
       </c>
       <c r="B77" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8109,42 +8104,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464194</v>
+        <v>464139</v>
       </c>
       <c r="R77" t="n">
-        <v>6788999</v>
+        <v>6788911</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8174,6 +8164,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8200,10 +8195,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131898908</v>
+        <v>131900596</v>
       </c>
       <c r="B78" t="n">
-        <v>79031</v>
+        <v>57914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8211,34 +8206,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464178</v>
+        <v>464194</v>
       </c>
       <c r="R78" t="n">
-        <v>6788843</v>
+        <v>6788999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131898976</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131897243</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131900374</v>
       </c>
       <c r="B4" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131897313</v>
       </c>
       <c r="B5" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>131902048</v>
       </c>
       <c r="B7" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>131902624</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131900839</v>
       </c>
       <c r="B9" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902053</v>
+        <v>131902908</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>78983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463710</v>
+        <v>463699</v>
       </c>
       <c r="R11" t="n">
-        <v>6788923</v>
+        <v>6788977</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902512</v>
+        <v>131902053</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463582</v>
+        <v>463710</v>
       </c>
       <c r="R12" t="n">
-        <v>6788856</v>
+        <v>6788923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902908</v>
+        <v>131902512</v>
       </c>
       <c r="B13" t="n">
-        <v>78981</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463699</v>
+        <v>463582</v>
       </c>
       <c r="R13" t="n">
-        <v>6788977</v>
+        <v>6788856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>131902164</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,45 +2252,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131898938</v>
+        <v>131898363</v>
       </c>
       <c r="B18" t="n">
-        <v>79339</v>
+        <v>57948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464168</v>
+        <v>464192</v>
       </c>
       <c r="R18" t="n">
-        <v>6788847</v>
+        <v>6788879</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131898363</v>
+        <v>131903093</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,39 +2365,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464192</v>
+        <v>463928</v>
       </c>
       <c r="R19" t="n">
-        <v>6788879</v>
+        <v>6789135</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,52 +2444,52 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131903093</v>
+        <v>131898938</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463928</v>
+        <v>464168</v>
       </c>
       <c r="R20" t="n">
-        <v>6789135</v>
+        <v>6788847</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131901655</v>
+        <v>131897316</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>81302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463892</v>
+        <v>464224</v>
       </c>
       <c r="R21" t="n">
-        <v>6789126</v>
+        <v>6788964</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131897316</v>
+        <v>131901655</v>
       </c>
       <c r="B22" t="n">
-        <v>81300</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464224</v>
+        <v>463892</v>
       </c>
       <c r="R22" t="n">
-        <v>6788964</v>
+        <v>6789126</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131900843</v>
+        <v>131900297</v>
       </c>
       <c r="B23" t="n">
-        <v>79905</v>
+        <v>78983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464154</v>
+        <v>464132</v>
       </c>
       <c r="R23" t="n">
-        <v>6789027</v>
+        <v>6788922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3052,45 +3052,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131900297</v>
+        <v>131900445</v>
       </c>
       <c r="B26" t="n">
-        <v>78981</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464132</v>
+        <v>464151</v>
       </c>
       <c r="R26" t="n">
-        <v>6788922</v>
+        <v>6788971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,50 +3154,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131900445</v>
+        <v>131900843</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>79907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464151</v>
+        <v>464154</v>
       </c>
       <c r="R27" t="n">
-        <v>6788971</v>
+        <v>6789027</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131901760</v>
+        <v>131899185</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,39 +3262,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463848</v>
+        <v>464113</v>
       </c>
       <c r="R28" t="n">
-        <v>6789114</v>
+        <v>6788858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,17 +3341,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131902263</v>
+        <v>131898255</v>
       </c>
       <c r="B29" t="n">
-        <v>79905</v>
+        <v>57948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,34 +3359,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463633</v>
+        <v>464199</v>
       </c>
       <c r="R29" t="n">
-        <v>6788814</v>
+        <v>6788859</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,6 +3426,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3443,17 +3448,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131899185</v>
+        <v>131902508</v>
       </c>
       <c r="B30" t="n">
-        <v>79315</v>
+        <v>78983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,34 +3466,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464113</v>
+        <v>463582</v>
       </c>
       <c r="R30" t="n">
-        <v>6788858</v>
+        <v>6788856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3540,17 +3545,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131898255</v>
+        <v>131902296</v>
       </c>
       <c r="B31" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,39 +3563,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464199</v>
+        <v>463633</v>
       </c>
       <c r="R31" t="n">
-        <v>6788859</v>
+        <v>6788814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131902296</v>
+        <v>131900413</v>
       </c>
       <c r="B32" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,14 +3685,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463633</v>
+        <v>464141</v>
       </c>
       <c r="R32" t="n">
-        <v>6788814</v>
+        <v>6788971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,11 +3727,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3749,17 +3744,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131900413</v>
+        <v>131901760</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3767,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464141</v>
+        <v>463848</v>
       </c>
       <c r="R33" t="n">
-        <v>6788971</v>
+        <v>6789114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131902508</v>
+        <v>131902263</v>
       </c>
       <c r="B34" t="n">
-        <v>78981</v>
+        <v>79907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463582</v>
+        <v>463633</v>
       </c>
       <c r="R34" t="n">
-        <v>6788856</v>
+        <v>6788814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
         <v>131902169</v>
       </c>
       <c r="B35" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>131900601</v>
       </c>
       <c r="B36" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,32 +4144,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131901653</v>
+        <v>131902458</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4179,13 +4179,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463892</v>
+        <v>463561</v>
       </c>
       <c r="R37" t="n">
-        <v>6789126</v>
+        <v>6788842</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4215,6 +4215,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4234,55 +4239,60 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131902458</v>
+        <v>131901996</v>
       </c>
       <c r="B38" t="n">
-        <v>79315</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463561</v>
+        <v>463740</v>
       </c>
       <c r="R38" t="n">
-        <v>6788842</v>
+        <v>6788944</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4312,11 +4322,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4343,10 +4348,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131901996</v>
+        <v>131901653</v>
       </c>
       <c r="B39" t="n">
-        <v>57136</v>
+        <v>91855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,39 +4359,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463740</v>
+        <v>463892</v>
       </c>
       <c r="R39" t="n">
-        <v>6788944</v>
+        <v>6789126</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4438,52 +4438,61 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131900207</v>
+        <v>131902617</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464122</v>
+        <v>463597</v>
       </c>
       <c r="R40" t="n">
-        <v>6788896</v>
+        <v>6788860</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4518,6 +4527,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tre torrtallar</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4535,7 +4549,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4545,7 +4559,7 @@
         <v>131900410</v>
       </c>
       <c r="B41" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4639,54 +4653,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131902617</v>
+        <v>131900207</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463597</v>
+        <v>464122</v>
       </c>
       <c r="R42" t="n">
-        <v>6788860</v>
+        <v>6788896</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,11 +4726,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tre torrtallar</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
         <v>131902911</v>
       </c>
       <c r="B43" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>131900448</v>
       </c>
       <c r="B44" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131901998</v>
+        <v>131898831</v>
       </c>
       <c r="B45" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4975,14 +4975,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463740</v>
+        <v>464177</v>
       </c>
       <c r="R45" t="n">
-        <v>6788944</v>
+        <v>6788855</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131900323</v>
+        <v>131898366</v>
       </c>
       <c r="B46" t="n">
-        <v>79347</v>
+        <v>79317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5052,21 +5052,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464130</v>
+        <v>464192</v>
       </c>
       <c r="R46" t="n">
-        <v>6788932</v>
+        <v>6788879</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131898831</v>
+        <v>131900323</v>
       </c>
       <c r="B47" t="n">
-        <v>79315</v>
+        <v>79349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464177</v>
+        <v>464130</v>
       </c>
       <c r="R47" t="n">
-        <v>6788855</v>
+        <v>6788932</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131898366</v>
+        <v>131901998</v>
       </c>
       <c r="B48" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464192</v>
+        <v>463740</v>
       </c>
       <c r="R48" t="n">
-        <v>6788879</v>
+        <v>6788944</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131902049</v>
+        <v>131899796</v>
       </c>
       <c r="B49" t="n">
-        <v>79073</v>
+        <v>57948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,34 +5343,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463710</v>
+        <v>464098</v>
       </c>
       <c r="R49" t="n">
-        <v>6788923</v>
+        <v>6788894</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5531,10 +5536,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131899796</v>
+        <v>131902049</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5542,39 +5547,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464098</v>
+        <v>463710</v>
       </c>
       <c r="R51" t="n">
-        <v>6788894</v>
+        <v>6788923</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,17 +5626,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131898971</v>
+        <v>131902988</v>
       </c>
       <c r="B52" t="n">
-        <v>78981</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,34 +5644,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464168</v>
+        <v>463793</v>
       </c>
       <c r="R52" t="n">
-        <v>6788847</v>
+        <v>6789072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131900856</v>
+        <v>131903258</v>
       </c>
       <c r="B53" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5741,39 +5741,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464154</v>
+        <v>464176</v>
       </c>
       <c r="R53" t="n">
-        <v>6789027</v>
+        <v>6789029</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5825,17 +5820,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131898074</v>
+        <v>131900856</v>
       </c>
       <c r="B54" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5843,37 +5838,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464189</v>
+        <v>464154</v>
       </c>
       <c r="R54" t="n">
-        <v>6788866</v>
+        <v>6789027</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5903,11 +5903,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5934,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131902988</v>
+        <v>131898971</v>
       </c>
       <c r="B55" t="n">
-        <v>79315</v>
+        <v>78983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5945,34 +5940,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463793</v>
+        <v>464168</v>
       </c>
       <c r="R55" t="n">
-        <v>6789072</v>
+        <v>6788847</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,17 +6019,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131903258</v>
+        <v>131898074</v>
       </c>
       <c r="B56" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6066,13 +6061,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464176</v>
+        <v>464189</v>
       </c>
       <c r="R56" t="n">
-        <v>6789029</v>
+        <v>6788866</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6102,6 +6097,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>131900329</v>
       </c>
       <c r="B57" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>131903171</v>
       </c>
       <c r="B58" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131899801</v>
+        <v>131897390</v>
       </c>
       <c r="B59" t="n">
-        <v>79315</v>
+        <v>78983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464098</v>
+        <v>464224</v>
       </c>
       <c r="R59" t="n">
-        <v>6788894</v>
+        <v>6788964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131900650</v>
+        <v>131899801</v>
       </c>
       <c r="B60" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464205</v>
+        <v>464098</v>
       </c>
       <c r="R60" t="n">
-        <v>6789008</v>
+        <v>6788894</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6490,11 +6490,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6514,17 +6509,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131897390</v>
+        <v>131900650</v>
       </c>
       <c r="B61" t="n">
-        <v>78981</v>
+        <v>79317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6527,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,13 +6551,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464224</v>
+        <v>464205</v>
       </c>
       <c r="R61" t="n">
-        <v>6788964</v>
+        <v>6789008</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6592,6 +6587,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6621,7 +6621,7 @@
         <v>131901955</v>
       </c>
       <c r="B62" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>131902815</v>
       </c>
       <c r="B63" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>131900379</v>
       </c>
       <c r="B64" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>131902904</v>
       </c>
       <c r="B65" t="n">
-        <v>97966</v>
+        <v>97969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7011,45 +7011,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131903090</v>
+        <v>131901744</v>
       </c>
       <c r="B66" t="n">
-        <v>79905</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463928</v>
+        <v>463848</v>
       </c>
       <c r="R66" t="n">
-        <v>6789135</v>
+        <v>6789114</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7108,50 +7113,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131901744</v>
+        <v>131903090</v>
       </c>
       <c r="B67" t="n">
-        <v>8455</v>
+        <v>79907</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463848</v>
+        <v>463928</v>
       </c>
       <c r="R67" t="n">
-        <v>6789114</v>
+        <v>6789135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
         <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>131898911</v>
       </c>
       <c r="B69" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>131901872</v>
       </c>
       <c r="B70" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>131897325</v>
       </c>
       <c r="B73" t="n">
-        <v>79339</v>
+        <v>79341</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>131898908</v>
       </c>
       <c r="B74" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>131902839</v>
       </c>
       <c r="B75" t="n">
-        <v>79339</v>
+        <v>79341</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>131901762</v>
       </c>
       <c r="B76" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>131900248</v>
       </c>
       <c r="B77" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -4047,45 +4047,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131900601</v>
+        <v>131901653</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464194</v>
+        <v>463892</v>
       </c>
       <c r="R36" t="n">
-        <v>6788999</v>
+        <v>6789126</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131902458</v>
+        <v>131900601</v>
       </c>
       <c r="B37" t="n">
         <v>79317</v>
@@ -4175,17 +4175,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463561</v>
+        <v>464194</v>
       </c>
       <c r="R37" t="n">
-        <v>6788842</v>
+        <v>6788999</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4215,11 +4215,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4239,60 +4234,55 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131901996</v>
+        <v>131902458</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463740</v>
+        <v>463561</v>
       </c>
       <c r="R38" t="n">
-        <v>6788944</v>
+        <v>6788842</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4322,6 +4312,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,10 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131901653</v>
+        <v>131901996</v>
       </c>
       <c r="B39" t="n">
-        <v>91855</v>
+        <v>57136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4359,34 +4354,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463892</v>
+        <v>463740</v>
       </c>
       <c r="R39" t="n">
-        <v>6789126</v>
+        <v>6788944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131897390</v>
+        <v>131900650</v>
       </c>
       <c r="B59" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,13 +6357,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464224</v>
+        <v>464205</v>
       </c>
       <c r="R59" t="n">
-        <v>6788964</v>
+        <v>6789008</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6393,6 +6393,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6419,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131899801</v>
+        <v>131897390</v>
       </c>
       <c r="B60" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6454,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464098</v>
+        <v>464224</v>
       </c>
       <c r="R60" t="n">
-        <v>6788894</v>
+        <v>6788964</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,14 +6514,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131900650</v>
+        <v>131899801</v>
       </c>
       <c r="B61" t="n">
         <v>79317</v>
@@ -6551,13 +6556,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464205</v>
+        <v>464098</v>
       </c>
       <c r="R61" t="n">
-        <v>6789008</v>
+        <v>6788894</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6587,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6611,39 +6611,39 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131901955</v>
+        <v>131902904</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>97969</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463761</v>
+        <v>463699</v>
       </c>
       <c r="R62" t="n">
-        <v>6789030</v>
+        <v>6788977</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,48 +6715,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131902815</v>
+        <v>131901744</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463654</v>
+        <v>463848</v>
       </c>
       <c r="R63" t="n">
-        <v>6788918</v>
+        <v>6789114</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6786,11 +6791,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131900379</v>
+        <v>131903090</v>
       </c>
       <c r="B64" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,34 +6828,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464130</v>
+        <v>463928</v>
       </c>
       <c r="R64" t="n">
-        <v>6788950</v>
+        <v>6789135</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,39 +6907,39 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131902904</v>
+        <v>131901955</v>
       </c>
       <c r="B65" t="n">
-        <v>97969</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463699</v>
+        <v>463761</v>
       </c>
       <c r="R65" t="n">
-        <v>6788977</v>
+        <v>6789030</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,53 +7011,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131901744</v>
+        <v>131902815</v>
       </c>
       <c r="B66" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463848</v>
+        <v>463654</v>
       </c>
       <c r="R66" t="n">
-        <v>6789114</v>
+        <v>6788918</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7087,6 +7082,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131903090</v>
+        <v>131900379</v>
       </c>
       <c r="B67" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7124,34 +7124,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463928</v>
+        <v>464130</v>
       </c>
       <c r="R67" t="n">
-        <v>6789135</v>
+        <v>6788950</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7203,17 +7203,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131897699</v>
+        <v>131900191</v>
       </c>
       <c r="B68" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,34 +7221,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464211</v>
+        <v>464122</v>
       </c>
       <c r="R68" t="n">
-        <v>6788946</v>
+        <v>6788896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7307,10 +7312,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131898911</v>
+        <v>131897699</v>
       </c>
       <c r="B69" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7318,21 +7323,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7342,10 +7347,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464178</v>
+        <v>464211</v>
       </c>
       <c r="R69" t="n">
-        <v>6788843</v>
+        <v>6788946</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7404,7 +7409,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131901872</v>
+        <v>131898911</v>
       </c>
       <c r="B70" t="n">
         <v>79317</v>
@@ -7435,17 +7440,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>463779</v>
+        <v>464178</v>
       </c>
       <c r="R70" t="n">
-        <v>6789025</v>
+        <v>6788843</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7475,11 +7480,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7499,17 +7499,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131900290</v>
+        <v>131901872</v>
       </c>
       <c r="B71" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7517,37 +7517,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>463779</v>
       </c>
       <c r="R71" t="n">
-        <v>6788922</v>
+        <v>6789025</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,6 +7577,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7596,17 +7601,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900191</v>
+        <v>131900290</v>
       </c>
       <c r="B72" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7614,39 +7619,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464122</v>
+        <v>464132</v>
       </c>
       <c r="R72" t="n">
-        <v>6788896</v>
+        <v>6788922</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131897325</v>
+        <v>131902839</v>
       </c>
       <c r="B73" t="n">
         <v>79341</v>
@@ -7736,17 +7736,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464224</v>
+        <v>463654</v>
       </c>
       <c r="R73" t="n">
-        <v>6788964</v>
+        <v>6788918</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7795,17 +7795,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131898908</v>
+        <v>131901762</v>
       </c>
       <c r="B74" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7813,34 +7813,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464178</v>
+        <v>463848</v>
       </c>
       <c r="R74" t="n">
-        <v>6788843</v>
+        <v>6789114</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7892,52 +7892,52 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131902839</v>
+        <v>131900248</v>
       </c>
       <c r="B75" t="n">
-        <v>79341</v>
+        <v>79317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>463654</v>
+        <v>464139</v>
       </c>
       <c r="R75" t="n">
-        <v>6788918</v>
+        <v>6788911</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -7972,6 +7972,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -7989,17 +7994,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131901762</v>
+        <v>131900596</v>
       </c>
       <c r="B76" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8007,34 +8012,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>463848</v>
+        <v>464194</v>
       </c>
       <c r="R76" t="n">
-        <v>6789114</v>
+        <v>6788999</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8086,39 +8096,39 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131900248</v>
+        <v>131897325</v>
       </c>
       <c r="B77" t="n">
-        <v>79317</v>
+        <v>79341</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8128,13 +8138,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464139</v>
+        <v>464224</v>
       </c>
       <c r="R77" t="n">
-        <v>6788911</v>
+        <v>6788964</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8164,11 +8174,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8195,10 +8200,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131900596</v>
+        <v>131898908</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>79074</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8206,39 +8211,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464194</v>
+        <v>464178</v>
       </c>
       <c r="R78" t="n">
-        <v>6788999</v>
+        <v>6788843</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131898976</v>
+        <v>131900374</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464168</v>
+        <v>464130</v>
       </c>
       <c r="R2" t="n">
-        <v>6788847</v>
+        <v>6788950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131897243</v>
+        <v>131898976</v>
       </c>
       <c r="B3" t="n">
         <v>79317</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464220</v>
+        <v>464168</v>
       </c>
       <c r="R3" t="n">
-        <v>6788950</v>
+        <v>6788847</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet. Rikligt med brandljud</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131900374</v>
+        <v>131897243</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464130</v>
+        <v>464220</v>
       </c>
       <c r="R4" t="n">
         <v>6788950</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet. Rikligt med brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131902984</v>
+        <v>131902164</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,39 +1967,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463793</v>
+        <v>463693</v>
       </c>
       <c r="R15" t="n">
-        <v>6789072</v>
+        <v>6788840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131902164</v>
+        <v>131902984</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>57948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,34 +2064,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463693</v>
+        <v>463793</v>
       </c>
       <c r="R16" t="n">
-        <v>6788840</v>
+        <v>6789072</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,50 +2252,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131898363</v>
+        <v>131898938</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>79341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464192</v>
+        <v>464168</v>
       </c>
       <c r="R18" t="n">
-        <v>6788879</v>
+        <v>6788847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,45 +2446,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131898938</v>
+        <v>131898363</v>
       </c>
       <c r="B20" t="n">
-        <v>79341</v>
+        <v>57948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464168</v>
+        <v>464192</v>
       </c>
       <c r="R20" t="n">
-        <v>6788847</v>
+        <v>6788879</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131899185</v>
+        <v>131902263</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,34 +3262,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464113</v>
+        <v>463633</v>
       </c>
       <c r="R28" t="n">
-        <v>6788858</v>
+        <v>6788814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131898255</v>
+        <v>131899185</v>
       </c>
       <c r="B29" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,39 +3359,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464199</v>
+        <v>464113</v>
       </c>
       <c r="R29" t="n">
-        <v>6788859</v>
+        <v>6788858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3419,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131902508</v>
+        <v>131898255</v>
       </c>
       <c r="B30" t="n">
-        <v>78983</v>
+        <v>57948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,34 +3456,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463582</v>
+        <v>464199</v>
       </c>
       <c r="R30" t="n">
-        <v>6788856</v>
+        <v>6788859</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,6 +3523,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902296</v>
+        <v>131902508</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463633</v>
+        <v>463582</v>
       </c>
       <c r="R31" t="n">
-        <v>6788814</v>
+        <v>6788856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,11 +3623,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3654,7 +3649,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131900413</v>
+        <v>131902296</v>
       </c>
       <c r="B32" t="n">
         <v>79317</v>
@@ -3685,14 +3680,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464141</v>
+        <v>463633</v>
       </c>
       <c r="R32" t="n">
-        <v>6788971</v>
+        <v>6788814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,6 +3722,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3744,17 +3744,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131901760</v>
+        <v>131900413</v>
       </c>
       <c r="B33" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,39 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463848</v>
+        <v>464141</v>
       </c>
       <c r="R33" t="n">
-        <v>6789114</v>
+        <v>6788971</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3846,17 +3841,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131902263</v>
+        <v>131901760</v>
       </c>
       <c r="B34" t="n">
-        <v>79907</v>
+        <v>57945</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3864,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463633</v>
+        <v>463848</v>
       </c>
       <c r="R34" t="n">
-        <v>6788814</v>
+        <v>6789114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -6618,32 +6618,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131902904</v>
+        <v>131901955</v>
       </c>
       <c r="B62" t="n">
-        <v>97969</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463699</v>
+        <v>463761</v>
       </c>
       <c r="R62" t="n">
-        <v>6788977</v>
+        <v>6789030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,53 +6715,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131901744</v>
+        <v>131902815</v>
       </c>
       <c r="B63" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463848</v>
+        <v>463654</v>
       </c>
       <c r="R63" t="n">
-        <v>6789114</v>
+        <v>6788918</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6791,6 +6786,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131903090</v>
+        <v>131900379</v>
       </c>
       <c r="B64" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,34 +6828,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>463928</v>
+        <v>464130</v>
       </c>
       <c r="R64" t="n">
-        <v>6789135</v>
+        <v>6788950</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,39 +6907,39 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131901955</v>
+        <v>131902904</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>97969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463761</v>
+        <v>463699</v>
       </c>
       <c r="R65" t="n">
-        <v>6789030</v>
+        <v>6788977</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,48 +7011,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131902815</v>
+        <v>131901744</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463654</v>
+        <v>463848</v>
       </c>
       <c r="R66" t="n">
-        <v>6788918</v>
+        <v>6789114</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7082,11 +7087,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131900379</v>
+        <v>131903090</v>
       </c>
       <c r="B67" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7124,34 +7124,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464130</v>
+        <v>463928</v>
       </c>
       <c r="R67" t="n">
-        <v>6788950</v>
+        <v>6789135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131902839</v>
+        <v>131897325</v>
       </c>
       <c r="B73" t="n">
         <v>79341</v>
@@ -7736,17 +7736,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>463654</v>
+        <v>464224</v>
       </c>
       <c r="R73" t="n">
-        <v>6788918</v>
+        <v>6788964</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7795,17 +7795,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131901762</v>
+        <v>131898908</v>
       </c>
       <c r="B74" t="n">
-        <v>79317</v>
+        <v>79074</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7813,34 +7813,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>463848</v>
+        <v>464178</v>
       </c>
       <c r="R74" t="n">
-        <v>6789114</v>
+        <v>6788843</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7892,52 +7892,52 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131900248</v>
+        <v>131902839</v>
       </c>
       <c r="B75" t="n">
-        <v>79317</v>
+        <v>79341</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464139</v>
+        <v>463654</v>
       </c>
       <c r="R75" t="n">
-        <v>6788911</v>
+        <v>6788918</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -7972,11 +7972,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -7994,17 +7989,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131900596</v>
+        <v>131901762</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8012,39 +8007,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464194</v>
+        <v>463848</v>
       </c>
       <c r="R76" t="n">
-        <v>6788999</v>
+        <v>6789114</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8096,39 +8086,39 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131897325</v>
+        <v>131900248</v>
       </c>
       <c r="B77" t="n">
-        <v>79341</v>
+        <v>79317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8138,13 +8128,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464224</v>
+        <v>464139</v>
       </c>
       <c r="R77" t="n">
-        <v>6788964</v>
+        <v>6788911</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8174,6 +8164,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8200,10 +8195,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131898908</v>
+        <v>131900596</v>
       </c>
       <c r="B78" t="n">
-        <v>79074</v>
+        <v>57948</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8211,34 +8206,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464178</v>
+        <v>464194</v>
       </c>
       <c r="R78" t="n">
-        <v>6788843</v>
+        <v>6788999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131897313</v>
+        <v>131902048</v>
       </c>
       <c r="B5" t="n">
-        <v>79907</v>
+        <v>79074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464224</v>
+        <v>463710</v>
       </c>
       <c r="R5" t="n">
-        <v>6788964</v>
+        <v>6788923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,57 +1061,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131898011</v>
+        <v>131900839</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>78324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464206</v>
+        <v>464154</v>
       </c>
       <c r="R6" t="n">
-        <v>6788891</v>
+        <v>6789027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131902048</v>
+        <v>131898011</v>
       </c>
       <c r="B7" t="n">
-        <v>79074</v>
+        <v>57136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463710</v>
+        <v>464206</v>
       </c>
       <c r="R7" t="n">
-        <v>6788923</v>
+        <v>6788891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131902624</v>
+        <v>131897313</v>
       </c>
       <c r="B8" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1278,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463597</v>
+        <v>464224</v>
       </c>
       <c r="R8" t="n">
-        <v>6788860</v>
+        <v>6788964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,17 +1357,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131900839</v>
+        <v>131902624</v>
       </c>
       <c r="B9" t="n">
-        <v>78324</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464154</v>
+        <v>463597</v>
       </c>
       <c r="R9" t="n">
-        <v>6789027</v>
+        <v>6788860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902908</v>
+        <v>131902053</v>
       </c>
       <c r="B11" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463699</v>
+        <v>463710</v>
       </c>
       <c r="R11" t="n">
-        <v>6788977</v>
+        <v>6788923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902053</v>
+        <v>131902512</v>
       </c>
       <c r="B12" t="n">
         <v>79317</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463710</v>
+        <v>463582</v>
       </c>
       <c r="R12" t="n">
-        <v>6788923</v>
+        <v>6788856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902512</v>
+        <v>131902984</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,34 +1768,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463582</v>
+        <v>463793</v>
       </c>
       <c r="R13" t="n">
-        <v>6788856</v>
+        <v>6789072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,50 +1859,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131898830</v>
+        <v>131902164</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464177</v>
+        <v>463693</v>
       </c>
       <c r="R14" t="n">
-        <v>6788855</v>
+        <v>6788840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,52 +1949,57 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131902164</v>
+        <v>131898830</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463693</v>
+        <v>464177</v>
       </c>
       <c r="R15" t="n">
-        <v>6788840</v>
+        <v>6788855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,17 +2051,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131902984</v>
+        <v>131902908</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>78983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,39 +2069,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463793</v>
+        <v>463699</v>
       </c>
       <c r="R16" t="n">
-        <v>6789072</v>
+        <v>6788977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,45 +2252,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131898938</v>
+        <v>131903093</v>
       </c>
       <c r="B18" t="n">
-        <v>79341</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464168</v>
+        <v>463928</v>
       </c>
       <c r="R18" t="n">
-        <v>6788847</v>
+        <v>6789135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,52 +2342,52 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131903093</v>
+        <v>131898938</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463928</v>
+        <v>464168</v>
       </c>
       <c r="R19" t="n">
-        <v>6789135</v>
+        <v>6788847</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2742,45 +2742,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131900297</v>
+        <v>131900445</v>
       </c>
       <c r="B23" t="n">
-        <v>78983</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464132</v>
+        <v>464151</v>
       </c>
       <c r="R23" t="n">
-        <v>6788922</v>
+        <v>6788971</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,54 +2946,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131898053</v>
+        <v>131900297</v>
       </c>
       <c r="B25" t="n">
-        <v>57136</v>
+        <v>78983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464192</v>
+        <v>464132</v>
       </c>
       <c r="R25" t="n">
-        <v>6788879</v>
+        <v>6788922</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3052,50 +3043,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131900445</v>
+        <v>131900843</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>79907</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464151</v>
+        <v>464154</v>
       </c>
       <c r="R26" t="n">
-        <v>6788971</v>
+        <v>6789027</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,45 +3140,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131900843</v>
+        <v>131898053</v>
       </c>
       <c r="B27" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464154</v>
+        <v>464192</v>
       </c>
       <c r="R27" t="n">
-        <v>6789027</v>
+        <v>6788879</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,6 +3220,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902263</v>
+        <v>131902508</v>
       </c>
       <c r="B28" t="n">
-        <v>79907</v>
+        <v>78983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463633</v>
+        <v>463582</v>
       </c>
       <c r="R28" t="n">
-        <v>6788814</v>
+        <v>6788856</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131899185</v>
+        <v>131902296</v>
       </c>
       <c r="B29" t="n">
         <v>79317</v>
@@ -3379,14 +3379,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464113</v>
+        <v>463633</v>
       </c>
       <c r="R29" t="n">
-        <v>6788858</v>
+        <v>6788814</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,6 +3421,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3438,17 +3443,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131898255</v>
+        <v>131900413</v>
       </c>
       <c r="B30" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,39 +3461,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464141</v>
       </c>
       <c r="R30" t="n">
-        <v>6788859</v>
+        <v>6788971</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3521,11 +3521,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,10 +3547,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131902508</v>
+        <v>131901760</v>
       </c>
       <c r="B31" t="n">
-        <v>78983</v>
+        <v>57945</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,34 +3558,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463582</v>
+        <v>463848</v>
       </c>
       <c r="R31" t="n">
-        <v>6788856</v>
+        <v>6789114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131902296</v>
+        <v>131902263</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3720,11 +3720,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3751,7 +3746,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131900413</v>
+        <v>131899185</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3786,10 +3781,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464141</v>
+        <v>464113</v>
       </c>
       <c r="R33" t="n">
-        <v>6788971</v>
+        <v>6788858</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,10 +3843,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131901760</v>
+        <v>131898255</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,16 +3854,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3879,19 +3874,19 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463848</v>
+        <v>464199</v>
       </c>
       <c r="R34" t="n">
-        <v>6789114</v>
+        <v>6788859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3926,6 +3921,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4047,45 +4047,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131901653</v>
+        <v>131900601</v>
       </c>
       <c r="B36" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463892</v>
+        <v>464194</v>
       </c>
       <c r="R36" t="n">
-        <v>6789126</v>
+        <v>6788999</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131900601</v>
+        <v>131902458</v>
       </c>
       <c r="B37" t="n">
         <v>79317</v>
@@ -4175,17 +4175,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464194</v>
+        <v>463561</v>
       </c>
       <c r="R37" t="n">
-        <v>6788999</v>
+        <v>6788842</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4215,6 +4215,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4234,39 +4239,39 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131902458</v>
+        <v>131901653</v>
       </c>
       <c r="B38" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4276,13 +4281,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463561</v>
+        <v>463892</v>
       </c>
       <c r="R38" t="n">
-        <v>6788842</v>
+        <v>6789126</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4312,11 +4317,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4445,54 +4445,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131902617</v>
+        <v>131900207</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463597</v>
+        <v>464122</v>
       </c>
       <c r="R40" t="n">
-        <v>6788860</v>
+        <v>6788896</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4527,11 +4518,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På tre torrtallar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4549,7 +4535,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4653,45 +4639,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131900207</v>
+        <v>131902617</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464122</v>
+        <v>463597</v>
       </c>
       <c r="R42" t="n">
-        <v>6788896</v>
+        <v>6788860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4721,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tre torrtallar</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5131,17 +5131,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131900323</v>
+        <v>131901998</v>
       </c>
       <c r="B47" t="n">
-        <v>79349</v>
+        <v>79317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5149,34 +5149,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464130</v>
+        <v>463740</v>
       </c>
       <c r="R47" t="n">
-        <v>6788932</v>
+        <v>6788944</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,17 +5228,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131901998</v>
+        <v>131900323</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,34 +5246,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463740</v>
+        <v>464130</v>
       </c>
       <c r="R48" t="n">
-        <v>6788944</v>
+        <v>6788932</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131899796</v>
+        <v>131902049</v>
       </c>
       <c r="B49" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,39 +5343,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464098</v>
+        <v>463710</v>
       </c>
       <c r="R49" t="n">
-        <v>6788894</v>
+        <v>6788923</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,14 +5422,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899308</v>
+        <v>131899796</v>
       </c>
       <c r="B50" t="n">
         <v>57948</v>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464087</v>
+        <v>464098</v>
       </c>
       <c r="R50" t="n">
-        <v>6788862</v>
+        <v>6788894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5536,10 +5531,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131902049</v>
+        <v>131899308</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>57948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5547,34 +5542,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463710</v>
+        <v>464087</v>
       </c>
       <c r="R51" t="n">
-        <v>6788923</v>
+        <v>6788862</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131900856</v>
+        <v>131898971</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>78983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,39 +5838,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464154</v>
+        <v>464168</v>
       </c>
       <c r="R54" t="n">
-        <v>6789027</v>
+        <v>6788847</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5929,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131898971</v>
+        <v>131898074</v>
       </c>
       <c r="B55" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,13 +5959,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464168</v>
+        <v>464189</v>
       </c>
       <c r="R55" t="n">
-        <v>6788847</v>
+        <v>6788866</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6000,6 +5995,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131898074</v>
+        <v>131900856</v>
       </c>
       <c r="B56" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,37 +6037,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464154</v>
       </c>
       <c r="R56" t="n">
-        <v>6788866</v>
+        <v>6789027</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6097,11 +6102,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6611,52 +6611,57 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131901955</v>
+        <v>131901744</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463761</v>
+        <v>463848</v>
       </c>
       <c r="R62" t="n">
-        <v>6789030</v>
+        <v>6789114</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131902815</v>
+        <v>131903090</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,13 +6755,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463654</v>
+        <v>463928</v>
       </c>
       <c r="R63" t="n">
-        <v>6788918</v>
+        <v>6789135</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6786,11 +6791,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,7 +6817,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131900379</v>
+        <v>131901955</v>
       </c>
       <c r="B64" t="n">
         <v>79317</v>
@@ -6848,14 +6848,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464130</v>
+        <v>463761</v>
       </c>
       <c r="R64" t="n">
-        <v>6788950</v>
+        <v>6789030</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,39 +6907,39 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131902904</v>
+        <v>131902815</v>
       </c>
       <c r="B65" t="n">
-        <v>97969</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463699</v>
+        <v>463654</v>
       </c>
       <c r="R65" t="n">
-        <v>6788977</v>
+        <v>6788918</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6985,6 +6985,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7011,50 +7016,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131901744</v>
+        <v>131900379</v>
       </c>
       <c r="B66" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>463848</v>
+        <v>464130</v>
       </c>
       <c r="R66" t="n">
-        <v>6789114</v>
+        <v>6788950</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,39 +7106,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131903090</v>
+        <v>131902904</v>
       </c>
       <c r="B67" t="n">
-        <v>79907</v>
+        <v>97969</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463928</v>
+        <v>463699</v>
       </c>
       <c r="R67" t="n">
-        <v>6789135</v>
+        <v>6788977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131900191</v>
+        <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,39 +7221,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464122</v>
+        <v>464211</v>
       </c>
       <c r="R68" t="n">
-        <v>6788896</v>
+        <v>6788946</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,10 +7307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131897699</v>
+        <v>131898911</v>
       </c>
       <c r="B69" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7323,21 +7318,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464211</v>
+        <v>464178</v>
       </c>
       <c r="R69" t="n">
-        <v>6788946</v>
+        <v>6788843</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,7 +7404,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131898911</v>
+        <v>131901872</v>
       </c>
       <c r="B70" t="n">
         <v>79317</v>
@@ -7440,17 +7435,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464178</v>
+        <v>463779</v>
       </c>
       <c r="R70" t="n">
-        <v>6788843</v>
+        <v>6789025</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7480,6 +7475,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7499,17 +7499,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131901872</v>
+        <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7517,37 +7517,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>463779</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6789025</v>
+        <v>6788922</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7577,11 +7577,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7601,17 +7596,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900290</v>
+        <v>131900191</v>
       </c>
       <c r="B72" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7619,34 +7614,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464132</v>
+        <v>464122</v>
       </c>
       <c r="R72" t="n">
-        <v>6788922</v>
+        <v>6788896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,45 +7705,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131897325</v>
+        <v>131900596</v>
       </c>
       <c r="B73" t="n">
-        <v>79341</v>
+        <v>57948</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464224</v>
+        <v>464194</v>
       </c>
       <c r="R73" t="n">
-        <v>6788964</v>
+        <v>6788999</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7802,32 +7807,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131898908</v>
+        <v>131897325</v>
       </c>
       <c r="B74" t="n">
-        <v>79074</v>
+        <v>79341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7837,10 +7842,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464178</v>
+        <v>464224</v>
       </c>
       <c r="R74" t="n">
-        <v>6788843</v>
+        <v>6788964</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7899,48 +7904,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131902839</v>
+        <v>131898908</v>
       </c>
       <c r="B75" t="n">
-        <v>79341</v>
+        <v>79074</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>463654</v>
+        <v>464178</v>
       </c>
       <c r="R75" t="n">
-        <v>6788918</v>
+        <v>6788843</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7989,39 +7994,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131901762</v>
+        <v>131902839</v>
       </c>
       <c r="B76" t="n">
-        <v>79317</v>
+        <v>79341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8031,13 +8036,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>463848</v>
+        <v>463654</v>
       </c>
       <c r="R76" t="n">
-        <v>6789114</v>
+        <v>6788918</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8093,7 +8098,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131900248</v>
+        <v>131901762</v>
       </c>
       <c r="B77" t="n">
         <v>79317</v>
@@ -8124,17 +8129,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464139</v>
+        <v>463848</v>
       </c>
       <c r="R77" t="n">
-        <v>6788911</v>
+        <v>6789114</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8164,11 +8169,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131900596</v>
+        <v>131900248</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8206,42 +8206,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464194</v>
+        <v>464139</v>
       </c>
       <c r="R78" t="n">
-        <v>6788999</v>
+        <v>6788911</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8271,6 +8266,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902053</v>
+        <v>131902908</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463710</v>
+        <v>463699</v>
       </c>
       <c r="R11" t="n">
-        <v>6788923</v>
+        <v>6788977</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902512</v>
+        <v>131902984</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,34 +1671,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463582</v>
+        <v>463793</v>
       </c>
       <c r="R12" t="n">
-        <v>6788856</v>
+        <v>6789072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,50 +1762,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902984</v>
+        <v>131898830</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463793</v>
+        <v>464177</v>
       </c>
       <c r="R13" t="n">
-        <v>6789072</v>
+        <v>6788855</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,17 +1857,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902164</v>
+        <v>131902053</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463693</v>
+        <v>463710</v>
       </c>
       <c r="R14" t="n">
-        <v>6788840</v>
+        <v>6788923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,50 +1961,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131898830</v>
+        <v>131902512</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464177</v>
+        <v>463582</v>
       </c>
       <c r="R15" t="n">
-        <v>6788855</v>
+        <v>6788856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,17 +2051,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131902908</v>
+        <v>131902164</v>
       </c>
       <c r="B16" t="n">
-        <v>78983</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463699</v>
+        <v>463693</v>
       </c>
       <c r="R16" t="n">
-        <v>6788977</v>
+        <v>6788840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131897316</v>
+        <v>131901655</v>
       </c>
       <c r="B21" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464224</v>
+        <v>463892</v>
       </c>
       <c r="R21" t="n">
-        <v>6788964</v>
+        <v>6789126</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131901655</v>
+        <v>131897316</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463892</v>
+        <v>464224</v>
       </c>
       <c r="R22" t="n">
-        <v>6789126</v>
+        <v>6788964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,38 +2742,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131900445</v>
+        <v>131899382</v>
       </c>
       <c r="B23" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464151</v>
+        <v>464087</v>
       </c>
       <c r="R23" t="n">
-        <v>6788971</v>
+        <v>6788862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2844,38 +2844,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131899382</v>
+        <v>131898053</v>
       </c>
       <c r="B24" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2884,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464087</v>
+        <v>464192</v>
       </c>
       <c r="R24" t="n">
-        <v>6788862</v>
+        <v>6788879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,6 +2924,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3043,45 +3052,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131900843</v>
+        <v>131900445</v>
       </c>
       <c r="B26" t="n">
-        <v>79907</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464154</v>
+        <v>464151</v>
       </c>
       <c r="R26" t="n">
-        <v>6789027</v>
+        <v>6788971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,54 +3154,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131898053</v>
+        <v>131900843</v>
       </c>
       <c r="B27" t="n">
-        <v>57136</v>
+        <v>79907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464192</v>
+        <v>464154</v>
       </c>
       <c r="R27" t="n">
-        <v>6788879</v>
+        <v>6789027</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3220,11 +3225,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spillning på flera platser i området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131902508</v>
+        <v>131902296</v>
       </c>
       <c r="B28" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463582</v>
+        <v>463633</v>
       </c>
       <c r="R28" t="n">
-        <v>6788856</v>
+        <v>6788814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,6 +3322,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3348,7 +3353,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131902296</v>
+        <v>131900413</v>
       </c>
       <c r="B29" t="n">
         <v>79317</v>
@@ -3379,14 +3384,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463633</v>
+        <v>464141</v>
       </c>
       <c r="R29" t="n">
-        <v>6788814</v>
+        <v>6788971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,11 +3426,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3443,17 +3443,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131900413</v>
+        <v>131901760</v>
       </c>
       <c r="B30" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3461,34 +3461,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464141</v>
+        <v>463848</v>
       </c>
       <c r="R30" t="n">
-        <v>6788971</v>
+        <v>6789114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3540,17 +3545,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131901760</v>
+        <v>131902263</v>
       </c>
       <c r="B31" t="n">
-        <v>57945</v>
+        <v>79907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,39 +3563,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463848</v>
+        <v>463633</v>
       </c>
       <c r="R31" t="n">
-        <v>6789114</v>
+        <v>6788814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131902263</v>
+        <v>131899185</v>
       </c>
       <c r="B32" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,34 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463633</v>
+        <v>464113</v>
       </c>
       <c r="R32" t="n">
-        <v>6788814</v>
+        <v>6788858</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131899185</v>
+        <v>131898255</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,34 +3757,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464113</v>
+        <v>464199</v>
       </c>
       <c r="R33" t="n">
-        <v>6788858</v>
+        <v>6788859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3817,6 +3822,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hål 2 meter upp, diameter 4,5 cm</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3843,10 +3853,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131898255</v>
+        <v>131902508</v>
       </c>
       <c r="B34" t="n">
-        <v>57948</v>
+        <v>78983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3854,39 +3864,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464199</v>
+        <v>463582</v>
       </c>
       <c r="R34" t="n">
-        <v>6788859</v>
+        <v>6788856</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,11 +3926,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hål 2 meter upp, diameter 4,5 cm</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131901653</v>
+        <v>131901996</v>
       </c>
       <c r="B38" t="n">
-        <v>91855</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,34 +4257,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463892</v>
+        <v>463740</v>
       </c>
       <c r="R38" t="n">
-        <v>6789126</v>
+        <v>6788944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,17 +4341,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131901996</v>
+        <v>131901653</v>
       </c>
       <c r="B39" t="n">
-        <v>57136</v>
+        <v>91855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,39 +4359,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463740</v>
+        <v>463892</v>
       </c>
       <c r="R39" t="n">
-        <v>6788944</v>
+        <v>6789126</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131898831</v>
+        <v>131901998</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -4975,14 +4975,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464177</v>
+        <v>463740</v>
       </c>
       <c r="R45" t="n">
-        <v>6788855</v>
+        <v>6788944</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131898366</v>
+        <v>131900323</v>
       </c>
       <c r="B46" t="n">
-        <v>79317</v>
+        <v>79349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5052,21 +5052,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464192</v>
+        <v>464130</v>
       </c>
       <c r="R46" t="n">
-        <v>6788879</v>
+        <v>6788932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,14 +5131,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131901998</v>
+        <v>131898831</v>
       </c>
       <c r="B47" t="n">
         <v>79317</v>
@@ -5169,14 +5169,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463740</v>
+        <v>464177</v>
       </c>
       <c r="R47" t="n">
-        <v>6788944</v>
+        <v>6788855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,17 +5228,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131900323</v>
+        <v>131898366</v>
       </c>
       <c r="B48" t="n">
-        <v>79349</v>
+        <v>79317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,21 +5246,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464130</v>
+        <v>464192</v>
       </c>
       <c r="R48" t="n">
-        <v>6788932</v>
+        <v>6788879</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6618,50 +6618,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131901744</v>
+        <v>131901955</v>
       </c>
       <c r="B62" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463848</v>
+        <v>463761</v>
       </c>
       <c r="R62" t="n">
-        <v>6789114</v>
+        <v>6789030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131903090</v>
+        <v>131902815</v>
       </c>
       <c r="B63" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,13 +6750,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>463928</v>
+        <v>463654</v>
       </c>
       <c r="R63" t="n">
-        <v>6789135</v>
+        <v>6788918</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6791,6 +6786,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,7 +6817,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131901955</v>
+        <v>131900379</v>
       </c>
       <c r="B64" t="n">
         <v>79317</v>
@@ -6848,14 +6848,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>463761</v>
+        <v>464130</v>
       </c>
       <c r="R64" t="n">
-        <v>6789030</v>
+        <v>6788950</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,55 +6907,60 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131902815</v>
+        <v>131901744</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>463654</v>
+        <v>463848</v>
       </c>
       <c r="R65" t="n">
-        <v>6788918</v>
+        <v>6789114</v>
       </c>
       <c r="S65" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6985,11 +6990,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131900379</v>
+        <v>131903090</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,34 +7027,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464130</v>
+        <v>463928</v>
       </c>
       <c r="R66" t="n">
-        <v>6788950</v>
+        <v>6789135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131897699</v>
+        <v>131901872</v>
       </c>
       <c r="B68" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,37 +7221,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464211</v>
+        <v>463779</v>
       </c>
       <c r="R68" t="n">
-        <v>6788946</v>
+        <v>6789025</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7281,6 +7281,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7300,17 +7305,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131898911</v>
+        <v>131900191</v>
       </c>
       <c r="B69" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7318,34 +7323,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464178</v>
+        <v>464122</v>
       </c>
       <c r="R69" t="n">
-        <v>6788843</v>
+        <v>6788896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7404,10 +7414,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131901872</v>
+        <v>131897699</v>
       </c>
       <c r="B70" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7415,37 +7425,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>463779</v>
+        <v>464211</v>
       </c>
       <c r="R70" t="n">
-        <v>6789025</v>
+        <v>6788946</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7475,11 +7485,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7499,17 +7504,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131900290</v>
+        <v>131898911</v>
       </c>
       <c r="B71" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7517,21 +7522,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7541,10 +7546,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464178</v>
       </c>
       <c r="R71" t="n">
-        <v>6788922</v>
+        <v>6788843</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7603,10 +7608,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900191</v>
+        <v>131900290</v>
       </c>
       <c r="B72" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7614,39 +7619,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464122</v>
+        <v>464132</v>
       </c>
       <c r="R72" t="n">
-        <v>6788896</v>
+        <v>6788922</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131901655</v>
+        <v>131897316</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463892</v>
+        <v>464224</v>
       </c>
       <c r="R21" t="n">
-        <v>6789126</v>
+        <v>6788964</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131897316</v>
+        <v>131901655</v>
       </c>
       <c r="B22" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464224</v>
+        <v>463892</v>
       </c>
       <c r="R22" t="n">
-        <v>6788964</v>
+        <v>6789126</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131901996</v>
+        <v>131901653</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>91855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,39 +4257,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463740</v>
+        <v>463892</v>
       </c>
       <c r="R38" t="n">
-        <v>6788944</v>
+        <v>6789126</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4341,17 +4336,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131901653</v>
+        <v>131901996</v>
       </c>
       <c r="B39" t="n">
-        <v>91855</v>
+        <v>57136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4359,34 +4354,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463892</v>
+        <v>463740</v>
       </c>
       <c r="R39" t="n">
-        <v>6789126</v>
+        <v>6788944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131901998</v>
+        <v>131898831</v>
       </c>
       <c r="B45" t="n">
         <v>79317</v>
@@ -4975,14 +4975,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463740</v>
+        <v>464177</v>
       </c>
       <c r="R45" t="n">
-        <v>6788944</v>
+        <v>6788855</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131900323</v>
+        <v>131898366</v>
       </c>
       <c r="B46" t="n">
-        <v>79349</v>
+        <v>79317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5052,21 +5052,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464130</v>
+        <v>464192</v>
       </c>
       <c r="R46" t="n">
-        <v>6788932</v>
+        <v>6788879</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,14 +5131,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131898831</v>
+        <v>131901998</v>
       </c>
       <c r="B47" t="n">
         <v>79317</v>
@@ -5169,14 +5169,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464177</v>
+        <v>463740</v>
       </c>
       <c r="R47" t="n">
-        <v>6788855</v>
+        <v>6788944</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,17 +5228,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131898366</v>
+        <v>131900323</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,21 +5246,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464192</v>
+        <v>464130</v>
       </c>
       <c r="R48" t="n">
-        <v>6788879</v>
+        <v>6788932</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131902049</v>
+        <v>131899796</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>57948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,34 +5343,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463710</v>
+        <v>464098</v>
       </c>
       <c r="R49" t="n">
-        <v>6788923</v>
+        <v>6788894</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,14 +5427,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899796</v>
+        <v>131899308</v>
       </c>
       <c r="B50" t="n">
         <v>57948</v>
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464098</v>
+        <v>464087</v>
       </c>
       <c r="R50" t="n">
-        <v>6788894</v>
+        <v>6788862</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5531,10 +5536,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131899308</v>
+        <v>131902049</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5542,39 +5547,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464087</v>
+        <v>463710</v>
       </c>
       <c r="R51" t="n">
-        <v>6788862</v>
+        <v>6788923</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131898971</v>
+        <v>131900856</v>
       </c>
       <c r="B54" t="n">
-        <v>78983</v>
+        <v>57945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,34 +5838,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464168</v>
+        <v>464154</v>
       </c>
       <c r="R54" t="n">
-        <v>6788847</v>
+        <v>6789027</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5924,10 +5929,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131898074</v>
+        <v>131898971</v>
       </c>
       <c r="B55" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5935,21 +5940,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,13 +5964,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464189</v>
+        <v>464168</v>
       </c>
       <c r="R55" t="n">
-        <v>6788866</v>
+        <v>6788847</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5995,11 +6000,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131900856</v>
+        <v>131898074</v>
       </c>
       <c r="B56" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,42 +6037,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464154</v>
+        <v>464189</v>
       </c>
       <c r="R56" t="n">
-        <v>6789027</v>
+        <v>6788866</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6102,6 +6097,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7210,10 +7210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131901872</v>
+        <v>131897699</v>
       </c>
       <c r="B68" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7221,37 +7221,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>463779</v>
+        <v>464211</v>
       </c>
       <c r="R68" t="n">
-        <v>6789025</v>
+        <v>6788946</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7281,11 +7281,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7305,17 +7300,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131900191</v>
+        <v>131898911</v>
       </c>
       <c r="B69" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7323,39 +7318,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464122</v>
+        <v>464178</v>
       </c>
       <c r="R69" t="n">
-        <v>6788896</v>
+        <v>6788843</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7414,10 +7404,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131897699</v>
+        <v>131901872</v>
       </c>
       <c r="B70" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7425,37 +7415,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464211</v>
+        <v>463779</v>
       </c>
       <c r="R70" t="n">
-        <v>6788946</v>
+        <v>6789025</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7485,6 +7475,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7504,17 +7499,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131898911</v>
+        <v>131900290</v>
       </c>
       <c r="B71" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7522,21 +7517,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7546,10 +7541,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464178</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6788843</v>
+        <v>6788922</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7608,10 +7603,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131900290</v>
+        <v>131900191</v>
       </c>
       <c r="B72" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7619,34 +7614,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464132</v>
+        <v>464122</v>
       </c>
       <c r="R72" t="n">
-        <v>6788922</v>
+        <v>6788896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 9083-2026 artfynd.xlsx
+++ b/artfynd/A 9083-2026 artfynd.xlsx
@@ -2548,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131897316</v>
+        <v>131901655</v>
       </c>
       <c r="B21" t="n">
-        <v>81302</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,34 +2559,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464224</v>
+        <v>463892</v>
       </c>
       <c r="R21" t="n">
-        <v>6788964</v>
+        <v>6789126</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131901655</v>
+        <v>131897316</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>81302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463892</v>
+        <v>464224</v>
       </c>
       <c r="R22" t="n">
-        <v>6789126</v>
+        <v>6788964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131901653</v>
+        <v>131901996</v>
       </c>
       <c r="B38" t="n">
-        <v>91855</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,34 +4257,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463892</v>
+        <v>463740</v>
       </c>
       <c r="R38" t="n">
-        <v>6789126</v>
+        <v>6788944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,17 +4341,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131901996</v>
+        <v>131901653</v>
       </c>
       <c r="B39" t="n">
-        <v>57136</v>
+        <v>91855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,39 +4359,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463740</v>
+        <v>463892</v>
       </c>
       <c r="R39" t="n">
-        <v>6788944</v>
+        <v>6789126</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131899796</v>
+        <v>131902049</v>
       </c>
       <c r="B49" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,39 +5343,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464098</v>
+        <v>463710</v>
       </c>
       <c r="R49" t="n">
-        <v>6788894</v>
+        <v>6788923</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,14 +5422,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131899308</v>
+        <v>131899796</v>
       </c>
       <c r="B50" t="n">
         <v>57948</v>
@@ -5474,10 +5469,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464087</v>
+        <v>464098</v>
       </c>
       <c r="R50" t="n">
-        <v>6788862</v>
+        <v>6788894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5536,10 +5531,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131902049</v>
+        <v>131899308</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>57948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5547,34 +5542,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463710</v>
+        <v>464087</v>
       </c>
       <c r="R51" t="n">
-        <v>6788923</v>
+        <v>6788862</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131900856</v>
+        <v>131898971</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>78983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5838,39 +5838,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464154</v>
+        <v>464168</v>
       </c>
       <c r="R54" t="n">
-        <v>6789027</v>
+        <v>6788847</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5929,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131898971</v>
+        <v>131898074</v>
       </c>
       <c r="B55" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5940,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,13 +5959,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464168</v>
+        <v>464189</v>
       </c>
       <c r="R55" t="n">
-        <v>6788847</v>
+        <v>6788866</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6000,6 +5995,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131898074</v>
+        <v>131900856</v>
       </c>
       <c r="B56" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,37 +6037,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464154</v>
       </c>
       <c r="R56" t="n">
-        <v>6788866</v>
+        <v>6789027</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6097,11 +6102,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131897390</v>
+        <v>131899801</v>
       </c>
       <c r="B60" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464224</v>
+        <v>464098</v>
       </c>
       <c r="R60" t="n">
-        <v>6788964</v>
+        <v>6788894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131899801</v>
+        <v>131897390</v>
       </c>
       <c r="B61" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464098</v>
+        <v>464224</v>
       </c>
       <c r="R61" t="n">
-        <v>6788894</v>
+        <v>6788964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
